--- a/data/trans_dic/P37A$vacunaempresa-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunaempresa-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,31</t>
+          <t>0,33; 3,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,02</t>
+          <t>0,56; 4,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,02</t>
+          <t>1,6; 6,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,63</t>
+          <t>0,34; 4,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,82</t>
+          <t>3,1; 7,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,98</t>
+          <t>0,35; 1,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,98</t>
+          <t>0,64; 3,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,5</t>
+          <t>0,15; 1,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,43</t>
+          <t>2,73; 5,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,32</t>
+          <t>0,52; 3,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,84</t>
+          <t>0,2; 1,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,54</t>
+          <t>0,24; 2,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,68</t>
+          <t>0,18; 1,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,9</t>
+          <t>0,19; 1,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,85</t>
+          <t>0,55; 2,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,96</t>
+          <t>0,1; 0,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,06</t>
+          <t>0,41; 1,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,41</t>
+          <t>0,31; 1,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,21</t>
+          <t>0,59; 2,02</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,17</t>
+          <t>0,87; 4,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,15</t>
+          <t>0,24; 2,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,32</t>
+          <t>0,27; 2,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,25; 2,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,71</t>
+          <t>4,12; 8,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,75</t>
+          <t>0,29; 1,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,28</t>
+          <t>0,56; 2,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,77</t>
+          <t>0,25; 1,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,32</t>
+          <t>2,41; 5,11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,31</t>
+          <t>0,49; 3,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,93</t>
+          <t>0,5; 2,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,72</t>
+          <t>0,27; 3,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,36</t>
+          <t>0,59; 4,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,33</t>
+          <t>0,25; 2,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,58</t>
+          <t>0,7; 3,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,52</t>
+          <t>1,62; 5,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,31</t>
+          <t>0,48; 2,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,73</t>
+          <t>0,78; 2,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,85</t>
+          <t>0,26; 1,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,75</t>
+          <t>1,38; 3,79</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,77</t>
+          <t>0,48; 5,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,69</t>
+          <t>0,47; 5,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,8</t>
+          <t>0,45; 3,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,87</t>
+          <t>2,12; 7,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,54</t>
+          <t>0,4; 3,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,7</t>
+          <t>0,2; 1,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,32</t>
+          <t>0,47; 3,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,38</t>
+          <t>0,67; 3,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,82</t>
+          <t>0,22; 2,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,62</t>
+          <t>1,4; 3,86</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,19</t>
+          <t>0,39; 4,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,91</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,35</t>
+          <t>3,21; 7,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,79</t>
+          <t>0,53; 2,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,73</t>
+          <t>1,88; 4,35</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,1</t>
+          <t>0,44; 2,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,72</t>
+          <t>0,29; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,7</t>
+          <t>1,63; 4,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,8</t>
+          <t>0,3; 1,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,13</t>
+          <t>0,14; 1,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,68</t>
+          <t>2,81; 5,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,54</t>
+          <t>0,53; 1,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,09</t>
+          <t>0,28; 1,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,89</t>
+          <t>0,09; 0,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,2</t>
+          <t>2,58; 4,41</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,38</t>
+          <t>0,76; 2,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,06</t>
+          <t>0,5; 2,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1712,47 +1712,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,58</t>
+          <t>3,53; 6,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,06</t>
+          <t>0,47; 1,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,35</t>
+          <t>0,24; 1,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,91</t>
+          <t>1,16; 2,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,29</t>
+          <t>0,41; 1,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,72</t>
+          <t>0,57; 1,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,7</t>
+          <t>0,12; 0,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,88</t>
+          <t>2,56; 4,31</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,47</t>
+          <t>0,75; 1,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1847,52 +1847,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,78</t>
+          <t>0,26; 0,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,2</t>
+          <t>2,18; 3,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,84</t>
+          <t>0,33; 0,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,23</t>
+          <t>0,58; 1,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,84</t>
+          <t>0,32; 0,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,54</t>
+          <t>2,7; 3,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,99</t>
+          <t>0,59; 1,02</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,41</t>
+          <t>0,87; 1,44</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,69</t>
+          <t>0,34; 0,71</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,28</t>
+          <t>2,57; 3,38</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15798</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28814</t>
+          <t>25543</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>946; 9047</t>
+          <t>907; 8603</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1702; 11849</t>
+          <t>1657; 13199</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5332</t>
+          <t>0; 6881</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5932; 24964</t>
+          <t>5104; 19780</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5385</t>
+          <t>0; 5309</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>989; 13307</t>
+          <t>976; 11914</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6529</t>
+          <t>0; 6519</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10088; 25532</t>
+          <t>9802; 23192</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1835; 10590</t>
+          <t>1860; 10539</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3626; 17368</t>
+          <t>3699; 18476</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>880; 8725</t>
+          <t>875; 7839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19036; 44677</t>
+          <t>17315; 35809</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>12213</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5331</t>
+          <t>0; 5860</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2521; 16773</t>
+          <t>2635; 18094</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1022; 9241</t>
+          <t>1014; 8184</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1374; 13193</t>
+          <t>1291; 12556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>894; 8486</t>
+          <t>897; 7959</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 10193</t>
+          <t>0; 9273</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1093; 9947</t>
+          <t>992; 9721</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3169; 14682</t>
+          <t>2983; 14713</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>974; 9559</t>
+          <t>980; 9135</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4206; 21231</t>
+          <t>4180; 20529</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3059; 14454</t>
+          <t>3157; 14508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6078; 22871</t>
+          <t>6310; 21758</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>21463</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>24154</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7851</t>
+          <t>0; 7406</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2817; 13515</t>
+          <t>2828; 13167</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8218</t>
+          <t>0; 8136</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>757; 6809</t>
+          <t>765; 7715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>900; 7796</t>
+          <t>907; 8498</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7363</t>
+          <t>0; 6399</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7162</t>
+          <t>833; 7161</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14073; 30414</t>
+          <t>14683; 30402</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1945; 11478</t>
+          <t>1917; 11955</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3732; 15140</t>
+          <t>3733; 14838</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1630; 11566</t>
+          <t>1653; 11868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15972; 35388</t>
+          <t>16231; 34346</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>18629</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1753; 11869</t>
+          <t>1752; 13551</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1924; 10963</t>
+          <t>1887; 11016</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1731; 13750</t>
+          <t>985; 12169</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2282; 13637</t>
+          <t>2187; 15005</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>941; 8652</t>
+          <t>942; 8676</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2047; 13936</t>
+          <t>2735; 13847</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7768</t>
+          <t>0; 8835</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5727; 21488</t>
+          <t>6847; 21817</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2883; 16847</t>
+          <t>3504; 16007</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5885; 20860</t>
+          <t>5976; 20534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1917; 13975</t>
+          <t>1954; 14857</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10474; 29553</t>
+          <t>10972; 30140</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>10130</t>
         </is>
       </c>
     </row>
@@ -3041,32 +3041,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1533; 11733</t>
+          <t>981; 11110</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1017; 12105</t>
+          <t>1009; 11854</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>957; 8025</t>
+          <t>955; 7866</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3880; 14063</t>
+          <t>4363; 14508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6832</t>
+          <t>0; 6125</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>896; 7777</t>
+          <t>883; 6940</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>387; 4390</t>
+          <t>456; 4216</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2591; 13644</t>
+          <t>1944; 13425</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2918; 14608</t>
+          <t>2876; 15538</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>955; 7830</t>
+          <t>955; 8732</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5179; 15823</t>
+          <t>6092; 16792</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>15841</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 9633</t>
+          <t>0; 9499</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1075; 14208</t>
+          <t>1067; 13244</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>856; 7845</t>
+          <t>0; 6734</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,37 +3274,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 7253</t>
+          <t>0; 7207</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4598</t>
+          <t>0; 4179</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8534; 21459</t>
+          <t>8462; 20707</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 10117</t>
+          <t>0; 9649</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2173; 15484</t>
+          <t>2919; 15508</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3950</t>
+          <t>0; 4863</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10305; 24897</t>
+          <t>10068; 23225</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26792</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45452</t>
+          <t>51745</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2854; 12905</t>
+          <t>2679; 12980</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2648; 11370</t>
+          <t>1938; 11968</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 8812</t>
+          <t>0; 7947</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10457; 29326</t>
+          <t>11750; 32454</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1902; 11487</t>
+          <t>1922; 10932</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>939; 7843</t>
+          <t>942; 7726</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 9283</t>
+          <t>0; 11161</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12483; 39713</t>
+          <t>21658; 42766</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5871; 19347</t>
+          <t>6648; 19939</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3780; 14841</t>
+          <t>3740; 14991</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1173; 12002</t>
+          <t>1168; 12428</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28307; 61912</t>
+          <t>38427; 65860</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33818</t>
+          <t>38771</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>47397</t>
+          <t>53954</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5564; 17703</t>
+          <t>5662; 18545</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3775; 16076</t>
+          <t>3876; 15870</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3680,47 +3680,47 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15476; 51801</t>
+          <t>28132; 51686</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 5787</t>
+          <t>0; 7586</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3973; 16956</t>
+          <t>3869; 16249</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1956; 11188</t>
+          <t>1966; 11012</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8594; 20880</t>
+          <t>9633; 22439</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6327; 19655</t>
+          <t>6332; 19804</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9245; 27554</t>
+          <t>9167; 26706</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1954; 11280</t>
+          <t>1962; 11146</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28879; 63934</t>
+          <t>41660; 70194</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>201011</t>
+          <t>212209</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>24270; 48014</t>
+          <t>24584; 48567</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>34617; 64547</t>
+          <t>34748; 64513</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9042; 26472</t>
+          <t>8886; 25994</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67409; 110563</t>
+          <t>77178; 116429</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11597; 28389</t>
+          <t>10996; 28172</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21545; 43891</t>
+          <t>20789; 44556</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11815; 29907</t>
+          <t>11466; 28883</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>86964; 131265</t>
+          <t>100735; 139588</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39283; 66045</t>
+          <t>39214; 68139</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>60565; 98393</t>
+          <t>61116; 100264</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23057; 47937</t>
+          <t>23846; 49113</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>170575; 235060</t>
+          <t>187093; 245828</t>
         </is>
       </c>
     </row>
